--- a/Carrer Tool.xlsx
+++ b/Carrer Tool.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25200" windowHeight="11730"/>
+    <workbookView windowWidth="25200" windowHeight="11130" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="127">
   <si>
     <t>Postman</t>
   </si>
@@ -115,6 +115,12 @@
     <t>Python base performance testing</t>
   </si>
   <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
     <t>Mobile App</t>
   </si>
   <si>
@@ -389,6 +395,18 @@
   </si>
   <si>
     <t>zema global data corporation</t>
+  </si>
+  <si>
+    <t>Primesoft</t>
+  </si>
+  <si>
+    <t>Neebal Technologies</t>
+  </si>
+  <si>
+    <t>AQM Technologies</t>
+  </si>
+  <si>
+    <t>Capco</t>
   </si>
   <si>
     <t>May I know the budgeted range for this role?”</t>
@@ -1815,96 +1833,106 @@
         <v>26</v>
       </c>
     </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1920,398 +1948,418 @@
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <sheetData>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>51</v>
+      <c r="A2" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>53</v>
+      <c r="A3" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>57</v>
+      <c r="A5" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>59</v>
+      <c r="A6" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>61</v>
+      <c r="A7" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>77</v>
+      <c r="A16" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>80</v>
+      <c r="A18" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>88</v>
+      <c r="A24" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>90</v>
+      <c r="A25" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E31" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" t="s">
-        <v>99</v>
+      <c r="A33" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="E33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" t="s">
-        <v>100</v>
+      <c r="A34" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E36" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E40" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E41" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E42" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E43" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E44" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E46" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E47" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E48" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E49" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2395,12 +2443,12 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
